--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -15,14 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answered in the BDOI FRS" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT entry and exit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change requests" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$4:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$4:$G$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Traceability'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FR items'!$A$4:$F$279</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FR items'!$4:$4</definedName>
@@ -32,7 +33,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Answered in the BDOI FRS'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'UAT entry and exit'!$A$4:$C$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'UAT entry and exit'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Change requests'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Change requests'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -397,7 +400,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -710,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E34"/>
+  <dimension ref="B4:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -744,7 +747,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-02 Operations Cashiering - FRS in BDOI's template v3.2</t>
+          <t>BRD-02 Operations Cashiering - FRS in BDOI's template v3.3</t>
         </is>
       </c>
     </row>
@@ -891,7 +894,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -902,7 +905,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Every FR item of the FRS v3.2 with its test cases</t>
+          <t>Every FR item of the FRS v3.3 with its test cases</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -917,7 +920,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Test cases of the FRS v3.2 with the execution columns</t>
+          <t>Test cases of the FRS v3.3 with the execution columns</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
@@ -954,25 +957,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>The change requests of the FRS v3.3 linked to their FR items and test cases</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="15" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Pass</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Fail</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr"/>
@@ -980,13 +990,21 @@
     <row r="31">
       <c r="B31" s="17" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="18" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1001,6 +1019,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1013,7 +1032,106 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1023,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1273,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>FR items of the FRS v3.2</t>
+          <t>FR items of the FRS v3.3</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr"/>
@@ -1722,8 +1840,112 @@
       <c r="C47" s="12" t="inlineStr"/>
       <c r="D47" s="12" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>CR No.</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Change request (FRS Appendix W.2, CR register, CR effort workbook)</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr"/>
+      <c r="D49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>BRD ID it extends</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>FR item or appendix</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>Test cases affected</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Test cases of this workbook to update</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Man-days (CR effort workbook)</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D47"/>
+  <autoFilter ref="A4:D53"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1810,11 +2032,11 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>12 with test cases of their FR items; the others (availability, recovery) in the non-functional test of the programme</t>
+          <t>14 with test cases of their FR items; the others (availability, recovery) in the non-functional test of the programme</t>
         </is>
       </c>
     </row>
@@ -1925,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3440,7 +3662,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Peak: 15th and 30th of the month; 07:30-18:00</t>
+          <t>Peak: 15th and 30th of the month; peak hours 08:00-17:30</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -3747,12 +3969,152 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-15</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Maintenance: As per bank standard</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional test of the programme (NFR-AVL-03)</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-16</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Disaster: Business continuity threshold: RTO 4 hours, RPO 24 hours</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional test of the programme (NFR-REC-01, NFR-REC-02)</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-17</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Sessions: Programme NFR 10.07 (Collections addendum): one session per device</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.01.02</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-OPS.002.02-AC01, TC-FRS-OPS.002.02-AC02, TC-FRS-OPS.002.03-AC01, TC-FRS-OPS.002.03-AC02, TC-FRS-OPS.002.04-AC01, TC-FRS-OPS.002.04-AC02, TC-FRS-OPS.002.05-AC01, TC-OP-001.1-01, TC-OP-001.2-01, TC-OP-001.2-02, TC-OP-002.1-01, TC-OP-002.2-01, TC-OP-002.3-01</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-18</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Audit source: Programme NFR 4.03 (CLM, CLXN, RI addenda): source / IP address in the audit log</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.08.03</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-CSH.08.03.01-AC01, TC-OP-024.1-01, TC-OP-024.2-01, TC-OP-024.2-02, TC-OP-024.3-01, TC-OP-024.3-02, TC-OP-024.4-01</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G54"/>
+  <autoFilter ref="A4:G58"/>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G554">
+  <conditionalFormatting sqref="A5:G558">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3798,7 +4160,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Every FR item of the FRS v3.2 with its test cases</t>
+          <t>Every FR item of the FRS v3.3 with its test cases</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11968,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Test cases of the FRS v3.2 with the execution columns</t>
+          <t>Test cases of the FRS v3.3 with the execution columns</t>
         </is>
       </c>
     </row>
@@ -11807,7 +12169,7 @@
       <c r="R5" s="12" t="inlineStr"/>
       <c r="S5" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -11890,7 +12252,7 @@
       <c r="R6" s="12" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -11973,7 +12335,7 @@
       <c r="R7" s="12" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12418,7 @@
       <c r="R8" s="12" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12501,7 @@
       <c r="R9" s="12" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12584,7 @@
       <c r="R10" s="12" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12667,7 @@
       <c r="R11" s="12" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12750,7 @@
       <c r="R12" s="12" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12833,7 @@
       <c r="R13" s="12" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12916,7 @@
       <c r="R14" s="12" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12999,7 @@
       <c r="R15" s="12" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12720,7 +13082,7 @@
       <c r="R16" s="12" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12803,7 +13165,7 @@
       <c r="R17" s="12" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12886,7 +13248,7 @@
       <c r="R18" s="12" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -12969,7 +13331,7 @@
       <c r="R19" s="12" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13414,7 @@
       <c r="R20" s="12" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13497,7 @@
       <c r="R21" s="12" t="inlineStr"/>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13580,7 @@
       <c r="R22" s="12" t="inlineStr"/>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13301,7 +13663,7 @@
       <c r="R23" s="12" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13746,7 @@
       <c r="R24" s="12" t="inlineStr"/>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13829,7 @@
       <c r="R25" s="12" t="inlineStr"/>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13912,7 @@
       <c r="R26" s="12" t="inlineStr"/>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13995,7 @@
       <c r="R27" s="12" t="inlineStr"/>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13716,7 +14078,7 @@
       <c r="R28" s="12" t="inlineStr"/>
       <c r="S28" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13799,7 +14161,7 @@
       <c r="R29" s="12" t="inlineStr"/>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13882,7 +14244,7 @@
       <c r="R30" s="12" t="inlineStr"/>
       <c r="S30" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -13965,7 +14327,7 @@
       <c r="R31" s="12" t="inlineStr"/>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14048,7 +14410,7 @@
       <c r="R32" s="12" t="inlineStr"/>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14493,7 @@
       <c r="R33" s="12" t="inlineStr"/>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14576,7 @@
       <c r="R34" s="12" t="inlineStr"/>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14659,7 @@
       <c r="R35" s="12" t="inlineStr"/>
       <c r="S35" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14742,7 @@
       <c r="R36" s="12" t="inlineStr"/>
       <c r="S36" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14463,7 +14825,7 @@
       <c r="R37" s="12" t="inlineStr"/>
       <c r="S37" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14908,7 @@
       <c r="R38" s="12" t="inlineStr"/>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14991,7 @@
       <c r="R39" s="12" t="inlineStr"/>
       <c r="S39" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14712,7 +15074,7 @@
       <c r="R40" s="12" t="inlineStr"/>
       <c r="S40" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14795,7 +15157,7 @@
       <c r="R41" s="12" t="inlineStr"/>
       <c r="S41" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14878,7 +15240,7 @@
       <c r="R42" s="12" t="inlineStr"/>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14961,7 +15323,7 @@
       <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15406,7 @@
       <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15489,7 @@
       <c r="R45" s="12" t="inlineStr"/>
       <c r="S45" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15572,7 @@
       <c r="R46" s="12" t="inlineStr"/>
       <c r="S46" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15655,7 @@
       <c r="R47" s="12" t="inlineStr"/>
       <c r="S47" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15738,7 @@
       <c r="R48" s="12" t="inlineStr"/>
       <c r="S48" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15821,7 @@
       <c r="R49" s="12" t="inlineStr"/>
       <c r="S49" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15542,7 +15904,7 @@
       <c r="R50" s="12" t="inlineStr"/>
       <c r="S50" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15987,7 @@
       <c r="R51" s="12" t="inlineStr"/>
       <c r="S51" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15708,7 +16070,7 @@
       <c r="R52" s="12" t="inlineStr"/>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15791,7 +16153,7 @@
       <c r="R53" s="12" t="inlineStr"/>
       <c r="S53" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15874,7 +16236,7 @@
       <c r="R54" s="12" t="inlineStr"/>
       <c r="S54" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -15957,7 +16319,7 @@
       <c r="R55" s="12" t="inlineStr"/>
       <c r="S55" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16402,7 @@
       <c r="R56" s="12" t="inlineStr"/>
       <c r="S56" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16485,7 @@
       <c r="R57" s="12" t="inlineStr"/>
       <c r="S57" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16568,7 @@
       <c r="R58" s="12" t="inlineStr"/>
       <c r="S58" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16651,7 @@
       <c r="R59" s="12" t="inlineStr"/>
       <c r="S59" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16734,7 @@
       <c r="R60" s="12" t="inlineStr"/>
       <c r="S60" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16817,7 @@
       <c r="R61" s="12" t="inlineStr"/>
       <c r="S61" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16900,7 @@
       <c r="R62" s="12" t="inlineStr"/>
       <c r="S62" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16621,7 +16983,7 @@
       <c r="R63" s="12" t="inlineStr"/>
       <c r="S63" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16704,7 +17066,7 @@
       <c r="R64" s="12" t="inlineStr"/>
       <c r="S64" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16787,7 +17149,7 @@
       <c r="R65" s="12" t="inlineStr"/>
       <c r="S65" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16870,7 +17232,7 @@
       <c r="R66" s="12" t="inlineStr"/>
       <c r="S66" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -16953,7 +17315,7 @@
       <c r="R67" s="12" t="inlineStr"/>
       <c r="S67" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17398,7 @@
       <c r="R68" s="12" t="inlineStr"/>
       <c r="S68" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17481,7 @@
       <c r="R69" s="12" t="inlineStr"/>
       <c r="S69" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17564,7 @@
       <c r="R70" s="12" t="inlineStr"/>
       <c r="S70" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17285,7 +17647,7 @@
       <c r="R71" s="12" t="inlineStr"/>
       <c r="S71" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17730,7 @@
       <c r="R72" s="12" t="inlineStr"/>
       <c r="S72" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17813,7 @@
       <c r="R73" s="12" t="inlineStr"/>
       <c r="S73" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17896,7 @@
       <c r="R74" s="12" t="inlineStr"/>
       <c r="S74" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17617,7 +17979,7 @@
       <c r="R75" s="12" t="inlineStr"/>
       <c r="S75" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17700,7 +18062,7 @@
       <c r="R76" s="12" t="inlineStr"/>
       <c r="S76" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17783,7 +18145,7 @@
       <c r="R77" s="12" t="inlineStr"/>
       <c r="S77" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17866,7 +18228,7 @@
       <c r="R78" s="12" t="inlineStr"/>
       <c r="S78" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -17949,7 +18311,7 @@
       <c r="R79" s="12" t="inlineStr"/>
       <c r="S79" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18394,7 @@
       <c r="R80" s="12" t="inlineStr"/>
       <c r="S80" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18115,7 +18477,7 @@
       <c r="R81" s="12" t="inlineStr"/>
       <c r="S81" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18198,7 +18560,7 @@
       <c r="R82" s="12" t="inlineStr"/>
       <c r="S82" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18281,7 +18643,7 @@
       <c r="R83" s="12" t="inlineStr"/>
       <c r="S83" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18726,7 @@
       <c r="R84" s="12" t="inlineStr"/>
       <c r="S84" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18809,7 @@
       <c r="R85" s="12" t="inlineStr"/>
       <c r="S85" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18892,7 @@
       <c r="R86" s="12" t="inlineStr"/>
       <c r="S86" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18613,7 +18975,7 @@
       <c r="R87" s="12" t="inlineStr"/>
       <c r="S87" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18696,7 +19058,7 @@
       <c r="R88" s="12" t="inlineStr"/>
       <c r="S88" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18779,7 +19141,7 @@
       <c r="R89" s="12" t="inlineStr"/>
       <c r="S89" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18862,7 +19224,7 @@
       <c r="R90" s="12" t="inlineStr"/>
       <c r="S90" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -18945,7 +19307,7 @@
       <c r="R91" s="12" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19028,7 +19390,7 @@
       <c r="R92" s="12" t="inlineStr"/>
       <c r="S92" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19111,7 +19473,7 @@
       <c r="R93" s="12" t="inlineStr"/>
       <c r="S93" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19556,7 @@
       <c r="R94" s="12" t="inlineStr"/>
       <c r="S94" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19639,7 @@
       <c r="R95" s="12" t="inlineStr"/>
       <c r="S95" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19722,7 @@
       <c r="R96" s="12" t="inlineStr"/>
       <c r="S96" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19443,7 +19805,7 @@
       <c r="R97" s="12" t="inlineStr"/>
       <c r="S97" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19526,7 +19888,7 @@
       <c r="R98" s="12" t="inlineStr"/>
       <c r="S98" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19971,7 @@
       <c r="R99" s="12" t="inlineStr"/>
       <c r="S99" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19692,7 +20054,7 @@
       <c r="R100" s="12" t="inlineStr"/>
       <c r="S100" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19775,7 +20137,7 @@
       <c r="R101" s="12" t="inlineStr"/>
       <c r="S101" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19858,7 +20220,7 @@
       <c r="R102" s="12" t="inlineStr"/>
       <c r="S102" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -19941,7 +20303,7 @@
       <c r="R103" s="12" t="inlineStr"/>
       <c r="S103" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20024,7 +20386,7 @@
       <c r="R104" s="12" t="inlineStr"/>
       <c r="S104" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20469,7 @@
       <c r="R105" s="12" t="inlineStr"/>
       <c r="S105" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20552,7 @@
       <c r="R106" s="12" t="inlineStr"/>
       <c r="S106" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20635,7 @@
       <c r="R107" s="12" t="inlineStr"/>
       <c r="S107" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20356,7 +20718,7 @@
       <c r="R108" s="12" t="inlineStr"/>
       <c r="S108" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20801,7 @@
       <c r="R109" s="12" t="inlineStr"/>
       <c r="S109" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20884,7 @@
       <c r="R110" s="12" t="inlineStr"/>
       <c r="S110" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20605,7 +20967,7 @@
       <c r="R111" s="12" t="inlineStr"/>
       <c r="S111" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20688,7 +21050,7 @@
       <c r="R112" s="12" t="inlineStr"/>
       <c r="S112" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20771,7 +21133,7 @@
       <c r="R113" s="12" t="inlineStr"/>
       <c r="S113" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20854,7 +21216,7 @@
       <c r="R114" s="12" t="inlineStr"/>
       <c r="S114" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -20937,7 +21299,7 @@
       <c r="R115" s="12" t="inlineStr"/>
       <c r="S115" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21382,7 @@
       <c r="R116" s="12" t="inlineStr"/>
       <c r="S116" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21103,7 +21465,7 @@
       <c r="R117" s="12" t="inlineStr"/>
       <c r="S117" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21548,7 @@
       <c r="R118" s="12" t="inlineStr"/>
       <c r="S118" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21269,7 +21631,7 @@
       <c r="R119" s="12" t="inlineStr"/>
       <c r="S119" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21714,7 @@
       <c r="R120" s="12" t="inlineStr"/>
       <c r="S120" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21435,7 +21797,7 @@
       <c r="R121" s="12" t="inlineStr"/>
       <c r="S121" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21880,7 @@
       <c r="R122" s="12" t="inlineStr"/>
       <c r="S122" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21963,7 @@
       <c r="R123" s="12" t="inlineStr"/>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21684,7 +22046,7 @@
       <c r="R124" s="12" t="inlineStr"/>
       <c r="S124" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21767,7 +22129,7 @@
       <c r="R125" s="12" t="inlineStr"/>
       <c r="S125" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21850,7 +22212,7 @@
       <c r="R126" s="12" t="inlineStr"/>
       <c r="S126" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -21933,7 +22295,7 @@
       <c r="R127" s="12" t="inlineStr"/>
       <c r="S127" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22378,7 @@
       <c r="R128" s="12" t="inlineStr"/>
       <c r="S128" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22461,7 @@
       <c r="R129" s="12" t="inlineStr"/>
       <c r="S129" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22182,7 +22544,7 @@
       <c r="R130" s="12" t="inlineStr"/>
       <c r="S130" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22627,7 @@
       <c r="R131" s="12" t="inlineStr"/>
       <c r="S131" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22710,7 @@
       <c r="R132" s="12" t="inlineStr"/>
       <c r="S132" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22431,7 +22793,7 @@
       <c r="R133" s="12" t="inlineStr"/>
       <c r="S133" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22514,7 +22876,7 @@
       <c r="R134" s="12" t="inlineStr"/>
       <c r="S134" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22597,7 +22959,7 @@
       <c r="R135" s="12" t="inlineStr"/>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22680,7 +23042,7 @@
       <c r="R136" s="12" t="inlineStr"/>
       <c r="S136" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22763,7 +23125,7 @@
       <c r="R137" s="12" t="inlineStr"/>
       <c r="S137" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22846,7 +23208,7 @@
       <c r="R138" s="12" t="inlineStr"/>
       <c r="S138" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -22929,7 +23291,7 @@
       <c r="R139" s="12" t="inlineStr"/>
       <c r="S139" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23012,7 +23374,7 @@
       <c r="R140" s="12" t="inlineStr"/>
       <c r="S140" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23095,7 +23457,7 @@
       <c r="R141" s="12" t="inlineStr"/>
       <c r="S141" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23540,7 @@
       <c r="R142" s="12" t="inlineStr"/>
       <c r="S142" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23623,7 @@
       <c r="R143" s="12" t="inlineStr"/>
       <c r="S143" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23344,7 +23706,7 @@
       <c r="R144" s="12" t="inlineStr"/>
       <c r="S144" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23427,7 +23789,7 @@
       <c r="R145" s="12" t="inlineStr"/>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23872,7 @@
       <c r="R146" s="12" t="inlineStr"/>
       <c r="S146" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23593,7 +23955,7 @@
       <c r="R147" s="12" t="inlineStr"/>
       <c r="S147" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23676,7 +24038,7 @@
       <c r="R148" s="12" t="inlineStr"/>
       <c r="S148" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23759,7 +24121,7 @@
       <c r="R149" s="12" t="inlineStr"/>
       <c r="S149" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23842,7 +24204,7 @@
       <c r="R150" s="12" t="inlineStr"/>
       <c r="S150" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -23925,7 +24287,7 @@
       <c r="R151" s="12" t="inlineStr"/>
       <c r="S151" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24008,7 +24370,7 @@
       <c r="R152" s="12" t="inlineStr"/>
       <c r="S152" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24091,7 +24453,7 @@
       <c r="R153" s="12" t="inlineStr"/>
       <c r="S153" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24536,7 @@
       <c r="R154" s="12" t="inlineStr"/>
       <c r="S154" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24619,7 @@
       <c r="R155" s="12" t="inlineStr"/>
       <c r="S155" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24340,7 +24702,7 @@
       <c r="R156" s="12" t="inlineStr"/>
       <c r="S156" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24423,7 +24785,7 @@
       <c r="R157" s="12" t="inlineStr"/>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24868,7 @@
       <c r="R158" s="12" t="inlineStr"/>
       <c r="S158" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24951,7 @@
       <c r="R159" s="12" t="inlineStr"/>
       <c r="S159" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24672,7 +25034,7 @@
       <c r="R160" s="12" t="inlineStr"/>
       <c r="S160" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24755,7 +25117,7 @@
       <c r="R161" s="12" t="inlineStr"/>
       <c r="S161" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24838,7 +25200,7 @@
       <c r="R162" s="12" t="inlineStr"/>
       <c r="S162" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -24921,7 +25283,7 @@
       <c r="R163" s="12" t="inlineStr"/>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25366,7 @@
       <c r="R164" s="12" t="inlineStr"/>
       <c r="S164" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25449,7 @@
       <c r="R165" s="12" t="inlineStr"/>
       <c r="S165" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25170,7 +25532,7 @@
       <c r="R166" s="12" t="inlineStr"/>
       <c r="S166" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25253,7 +25615,7 @@
       <c r="R167" s="12" t="inlineStr"/>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25336,7 +25698,7 @@
       <c r="R168" s="12" t="inlineStr"/>
       <c r="S168" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25781,7 @@
       <c r="R169" s="12" t="inlineStr"/>
       <c r="S169" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25860,7 @@
       <c r="R170" s="12" t="inlineStr"/>
       <c r="S170" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25939,7 @@
       <c r="R171" s="12" t="inlineStr"/>
       <c r="S171" s="12" t="inlineStr">
         <is>
-          <t>Acceptance criterion of the FRS v3.2</t>
+          <t>Acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -37016,85 +37378,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C1" s="26" t="inlineStr">
-        <is>
-          <t>Result</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Change requests</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>Not run</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>The change requests of the FRS v3.3 linked to their FR items and test cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>CR No.</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Test cases affected</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-101</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Time rules of the Cashiering stages: overdue marker and reminder</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Appendix J (time rules); FRS.CSH.02.05, FRS.CSH.03.01, FRS.CSH.04.01, FRS.CSH.06.02</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>TC-OP-002.1-01, TC-OP-002.2-01, TC-OP-002.3-01, TC-OP-010.1-01, TC-OP-010.2-01, TC-OP-010.2-02, TC-OP-010.2-03, TC-OP-010.3-01, TC-OP-011.4-01, TC-OP-011.4-02, TC-OP-011.4-03, TC-OP-011.4-04, TC-OP-011.1-01, TC-OP-011.2-01, TC-OP-011.2-02, TC-OP-011.3-01, TC-OP-011.3-02, TC-OP-013.1-01, TC-OP-013.2-01, TC-OP-013.3-01</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-102</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>E-mail to a recipient list when a scheduled Cashiering run fails</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>BRQID.006 (extends)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.10.03; Appendix G (failed batch run)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-CSH.10.03.01-AC01, TC-FRS-CSH.10.03.01-AC02, TC-OP-008.1-01, TC-OP-008.2-01, TC-OP-008.3-01, TC-OP-008.3-02</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-103</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Excel export of the Cashiering lists</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>CSHID.023 (extends)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.01.03.04</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-CSH.01.03.04-AC01, TC-FRS-CSH.01.03.04-AC02, TC-OP-003.4-01, TC-OP-003.1-01, TC-OP-003.2-01, TC-OP-003.3-01, TC-OP-022.4-01, TC-OP-022.1-01, TC-OP-022.2-01, TC-OP-022.2-02, TC-OP-022.3-01, TC-OP-022.3-02, TC-OP-022.3-03</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-104</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Appendix G (channel of each notice)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>To be written if the change is approved</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:F508">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Answered in the BDOI FRS'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'UAT entry and exit'!$A$4:$C$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'UAT entry and exit'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Change requests'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Change requests'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Change requests'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -37378,7 +37378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37481,94 +37481,34 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>E-mail to a recipient list when a scheduled Cashiering run fails</t>
+          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>BRQID.006 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>FRS.CSH.10.03; Appendix G (failed batch run)</t>
+          <t>Appendix G (channel of each notice)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.10.03.01-AC01, TC-FRS-CSH.10.03.01-AC02, TC-OP-008.1-01, TC-OP-008.2-01, TC-OP-008.3-01, TC-OP-008.3-02</t>
+          <t>To be written if the change is approved</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>CR-CSH-103</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Excel export of the Cashiering lists</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>CSHID.023 (extends)</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.03.04</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>TC-FRS-CSH.01.03.04-AC01, TC-FRS-CSH.01.03.04-AC02, TC-OP-003.4-01, TC-OP-003.1-01, TC-OP-003.2-01, TC-OP-003.3-01, TC-OP-022.4-01, TC-OP-022.1-01, TC-OP-022.2-01, TC-OP-022.2-02, TC-OP-022.3-01, TC-OP-022.3-02, TC-OP-022.3-03</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>CR-CSH-104</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Appendix G (channel of each notice)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>To be written if the change is approved</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
         <v>3.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F8"/>
+  <autoFilter ref="A4:F6"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F508">
+  <conditionalFormatting sqref="A5:F506">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -723,13 +723,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -758,6 +761,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -830,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -972,6 +977,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
@@ -1003,6 +1009,8 @@
       </c>
       <c r="C32" s="16" t="inlineStr"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -1164,6 +1172,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -1033,7 +1033,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1133,7 +1133,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1959,7 +1959,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2140,7 +2140,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4132,7 +4132,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -11927,7 +11927,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="H223" s="12" t="inlineStr">
         <is>
-          <t>The test lead drops a Bills Payment file of the channel simulator in the MFT folder.</t>
+          <t>The test lead drops a Bills Payment test file of BDOI's systems (provided under the Integration scope) in the MFT folder.</t>
         </is>
       </c>
       <c r="I223" s="12" t="inlineStr">
@@ -36330,7 +36330,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37147,7 +37147,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37371,7 +37371,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37526,7 +37526,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_RTM_BRD-02_Test_Cases_and_Traceability_v1.0.xlsx
@@ -36328,7 +36328,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
